--- a/dados/gerencial/consolidado_gerencial_2025.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2025.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>529</v>
+        <v>536</v>
       </c>
       <c r="D4" t="n">
         <v>234</v>
       </c>
       <c r="E4" t="n">
-        <v>3411997.53</v>
+        <v>3532966.51</v>
       </c>
       <c r="F4" t="n">
-        <v>2112167.44</v>
+        <v>2132093.65</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45701</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="5">
@@ -516,19 +516,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>335</v>
+        <v>373</v>
       </c>
       <c r="D5" t="n">
         <v>69</v>
       </c>
       <c r="E5" t="n">
-        <v>1824473.65</v>
+        <v>2098790.69</v>
       </c>
       <c r="F5" t="n">
-        <v>1297110.62</v>
+        <v>1271759.14</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45702</v>
+        <v>45698</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="D6" t="n">
         <v>26</v>
       </c>
       <c r="E6" t="n">
-        <v>305902.49</v>
+        <v>351976.03</v>
       </c>
       <c r="F6" t="n">
-        <v>212443.04</v>
+        <v>218287.3</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45702</v>
+        <v>45700</v>
       </c>
     </row>
     <row r="7">
@@ -566,16 +566,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>458</v>
+        <v>521</v>
       </c>
       <c r="D7" t="n">
         <v>225</v>
       </c>
       <c r="E7" t="n">
-        <v>2630245.75</v>
+        <v>3016819.76</v>
       </c>
       <c r="F7" t="n">
-        <v>1986898.22</v>
+        <v>1688029.24</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>45729</v>
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>393</v>
+        <v>332</v>
       </c>
       <c r="D8" t="n">
         <v>50</v>
       </c>
       <c r="E8" t="n">
-        <v>2167651.5</v>
+        <v>1839122.68</v>
       </c>
       <c r="F8" t="n">
-        <v>1253198.95</v>
+        <v>1275263.97</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>45730</v>
+        <v>45728</v>
       </c>
     </row>
     <row r="9">
@@ -622,13 +622,13 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>376416.64</v>
+        <v>422224.07</v>
       </c>
       <c r="F9" t="n">
-        <v>246873.36</v>
+        <v>252450.26</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45726</v>
+        <v>45727</v>
       </c>
     </row>
     <row r="10">
@@ -641,16 +641,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="D10" t="n">
         <v>212</v>
       </c>
       <c r="E10" t="n">
-        <v>2892712.45</v>
+        <v>3337280.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1955286.27</v>
+        <v>1942694.21</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>45756</v>
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="D11" t="n">
         <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>1871182.26</v>
+        <v>1889536.5</v>
       </c>
       <c r="F11" t="n">
-        <v>1297633.18</v>
+        <v>1301455.28</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45758</v>
+        <v>45756</v>
       </c>
     </row>
     <row r="12">
@@ -697,13 +697,13 @@
         <v>24</v>
       </c>
       <c r="E12" t="n">
-        <v>433257.5</v>
+        <v>488147.58</v>
       </c>
       <c r="F12" t="n">
-        <v>327803.22</v>
+        <v>290600.25</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45758</v>
+        <v>45755</v>
       </c>
     </row>
     <row r="13">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="D13" t="n">
         <v>246</v>
       </c>
       <c r="E13" t="n">
-        <v>2813361.59</v>
+        <v>2903636.99</v>
       </c>
       <c r="F13" t="n">
-        <v>1908948.55</v>
+        <v>1909691.88</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>45789</v>
@@ -741,19 +741,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>351</v>
+        <v>409</v>
       </c>
       <c r="D14" t="n">
         <v>49</v>
       </c>
       <c r="E14" t="n">
-        <v>2015254.04</v>
+        <v>1970086.15</v>
       </c>
       <c r="F14" t="n">
-        <v>1352950.66</v>
+        <v>1315721.71</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>45789</v>
+        <v>45786</v>
       </c>
     </row>
     <row r="15">
@@ -766,19 +766,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
         <v>28</v>
       </c>
       <c r="E15" t="n">
-        <v>436955.16</v>
+        <v>505478.08</v>
       </c>
       <c r="F15" t="n">
-        <v>300656.12</v>
+        <v>297683.86</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>45791</v>
+        <v>45789</v>
       </c>
     </row>
     <row r="16">
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>481</v>
+        <v>564</v>
       </c>
       <c r="D16" t="n">
         <v>224</v>
       </c>
       <c r="E16" t="n">
-        <v>2878344.76</v>
+        <v>2928840.95</v>
       </c>
       <c r="F16" t="n">
-        <v>2035035.78</v>
+        <v>1955113.16</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45824</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="17">
@@ -816,19 +816,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>341</v>
+        <v>391</v>
       </c>
       <c r="D17" t="n">
         <v>43</v>
       </c>
       <c r="E17" t="n">
-        <v>1944247.94</v>
+        <v>1922115.48</v>
       </c>
       <c r="F17" t="n">
-        <v>1357114.71</v>
+        <v>1344220.26</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45820</v>
+        <v>45824</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D18" t="n">
         <v>30</v>
       </c>
       <c r="E18" t="n">
-        <v>484141.03</v>
+        <v>424425.39</v>
       </c>
       <c r="F18" t="n">
-        <v>306224.53</v>
+        <v>304452.56</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45824</v>
+        <v>45817</v>
       </c>
     </row>
     <row r="19">
@@ -866,16 +866,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>513</v>
+        <v>589</v>
       </c>
       <c r="D19" t="n">
         <v>235</v>
       </c>
       <c r="E19" t="n">
-        <v>2997620.48</v>
+        <v>3005538.88</v>
       </c>
       <c r="F19" t="n">
-        <v>2087944.47</v>
+        <v>2047974.02</v>
       </c>
       <c r="G19" s="3" t="n">
         <v>45848</v>
@@ -897,10 +897,10 @@
         <v>46</v>
       </c>
       <c r="E20" t="n">
-        <v>1993950.31</v>
+        <v>2018983.2</v>
       </c>
       <c r="F20" t="n">
-        <v>1311615.05</v>
+        <v>1325692.87</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>45852</v>
@@ -916,19 +916,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
         <v>29</v>
       </c>
       <c r="E21" t="n">
-        <v>484126.62</v>
+        <v>546367.04</v>
       </c>
       <c r="F21" t="n">
-        <v>324828.45</v>
+        <v>327259.82</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45848</v>
+        <v>45852</v>
       </c>
     </row>
     <row r="22">
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>516</v>
+        <v>608</v>
       </c>
       <c r="D22" t="n">
         <v>242</v>
       </c>
       <c r="E22" t="n">
-        <v>3600553.71</v>
+        <v>3668945.2</v>
       </c>
       <c r="F22" t="n">
-        <v>2198250.25</v>
+        <v>2187305.04</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45877</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="23">
@@ -966,19 +966,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D23" t="n">
         <v>48</v>
       </c>
       <c r="E23" t="n">
-        <v>1962409.38</v>
+        <v>1999000.72</v>
       </c>
       <c r="F23" t="n">
-        <v>1354384.13</v>
+        <v>1341956.98</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>45881</v>
+        <v>45880</v>
       </c>
     </row>
     <row r="24">
@@ -991,16 +991,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D24" t="n">
         <v>35</v>
       </c>
       <c r="E24" t="n">
-        <v>540738.98</v>
+        <v>458140.23</v>
       </c>
       <c r="F24" t="n">
-        <v>337199.45</v>
+        <v>328197.73</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>45880</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>643</v>
+        <v>649</v>
       </c>
       <c r="D25" t="n">
         <v>249</v>
       </c>
       <c r="E25" t="n">
-        <v>3751425.95</v>
+        <v>3824444.92</v>
       </c>
       <c r="F25" t="n">
-        <v>2536646.23</v>
+        <v>2617254.26</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45915</v>
+        <v>45910</v>
       </c>
     </row>
     <row r="26">
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D26" t="n">
         <v>59</v>
       </c>
       <c r="E26" t="n">
-        <v>2299139.65</v>
+        <v>1921418.46</v>
       </c>
       <c r="F26" t="n">
-        <v>1541083.15</v>
+        <v>1310374.26</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>45915</v>
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D27" t="n">
         <v>35</v>
       </c>
       <c r="E27" t="n">
-        <v>612063.4399999999</v>
+        <v>514526.68</v>
       </c>
       <c r="F27" t="n">
-        <v>426644.11</v>
+        <v>353244.92</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>45911</v>
@@ -1091,19 +1091,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>584</v>
+        <v>653</v>
       </c>
       <c r="D28" t="n">
         <v>295</v>
       </c>
       <c r="E28" t="n">
-        <v>3426025.68</v>
+        <v>3416423.43</v>
       </c>
       <c r="F28" t="n">
-        <v>2283357.5</v>
+        <v>2341161.61</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>45939</v>
+        <v>45945</v>
       </c>
     </row>
     <row r="29">
@@ -1116,16 +1116,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>327</v>
+        <v>386</v>
       </c>
       <c r="D29" t="n">
         <v>73</v>
       </c>
       <c r="E29" t="n">
-        <v>2228151.76</v>
+        <v>1907384.46</v>
       </c>
       <c r="F29" t="n">
-        <v>1528654.01</v>
+        <v>1295419.57</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>45943</v>
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D30" t="n">
         <v>42</v>
       </c>
       <c r="E30" t="n">
-        <v>605061.17</v>
+        <v>520509.66</v>
       </c>
       <c r="F30" t="n">
-        <v>412419.53</v>
+        <v>359354.65</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45945</v>
+        <v>45943</v>
       </c>
     </row>
     <row r="31">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="D31" t="n">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E31" t="n">
-        <v>3665641.31</v>
+        <v>4192489.84</v>
       </c>
       <c r="F31" t="n">
-        <v>2639759.86</v>
+        <v>2650571.59</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45975</v>
+        <v>45971</v>
       </c>
     </row>
     <row r="32">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="D32" t="n">
         <v>62</v>
       </c>
       <c r="E32" t="n">
-        <v>2338124.39</v>
+        <v>2008096.57</v>
       </c>
       <c r="F32" t="n">
-        <v>1380530.32</v>
+        <v>1392218.12</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
     </row>
     <row r="33">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D33" t="n">
         <v>42</v>
       </c>
       <c r="E33" t="n">
-        <v>536884.74</v>
+        <v>588815.29</v>
       </c>
       <c r="F33" t="n">
-        <v>373587.98</v>
+        <v>411677.58</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45974</v>
+        <v>45972</v>
       </c>
     </row>
     <row r="34">
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="D34" t="n">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E34" t="n">
-        <v>4449269.02</v>
+        <v>4430633.94</v>
       </c>
       <c r="F34" t="n">
-        <v>2556712.64</v>
+        <v>2650434.83</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>46000</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="35">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>344</v>
+        <v>404</v>
       </c>
       <c r="D35" t="n">
         <v>57</v>
       </c>
       <c r="E35" t="n">
-        <v>2029596.27</v>
+        <v>2327187.67</v>
       </c>
       <c r="F35" t="n">
-        <v>1333831.59</v>
+        <v>1362486.13</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
     </row>
     <row r="36">
@@ -1291,19 +1291,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="D36" t="n">
         <v>35</v>
       </c>
       <c r="E36" t="n">
-        <v>644804.55</v>
+        <v>558457.87</v>
       </c>
       <c r="F36" t="n">
-        <v>373905.66</v>
+        <v>379868.27</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>46006</v>
+        <v>46003</v>
       </c>
     </row>
     <row r="37">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="D37" t="n">
         <v>277</v>
       </c>
       <c r="E37" t="n">
-        <v>4634980.54</v>
+        <v>3913470.53</v>
       </c>
       <c r="F37" t="n">
-        <v>3168572.41</v>
+        <v>2796109.6</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
     </row>
     <row r="38">
@@ -1341,19 +1341,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D38" t="n">
         <v>79</v>
       </c>
       <c r="E38" t="n">
-        <v>2075679.33</v>
+        <v>2014469.36</v>
       </c>
       <c r="F38" t="n">
-        <v>1399149.05</v>
+        <v>1366824.67</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>46035</v>
+        <v>46030</v>
       </c>
     </row>
     <row r="39">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D39" t="n">
         <v>41</v>
       </c>
       <c r="E39" t="n">
-        <v>602648.47</v>
+        <v>601902.65</v>
       </c>
       <c r="F39" t="n">
-        <v>423411.97</v>
+        <v>422185.59</v>
       </c>
       <c r="G39" s="3" t="n">
         <v>46034</v>
@@ -1391,10 +1391,10 @@
         <v>4113</v>
       </c>
       <c r="E40" t="n">
-        <v>71965040.04000001</v>
+        <v>72068653.86</v>
       </c>
       <c r="F40" t="n">
-        <v>47942832.46</v>
+        <v>46767088.84</v>
       </c>
     </row>
   </sheetData>
